--- a/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rcp/rcp_tax_ci.xlsx
+++ b/HMS-TAX_Updated/HMS-TAX/bin/Debug/Reports/rcp/rcp_tax_ci.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Dev\HMS-TAX\HMS-TAX\bin\Debug\Reports\rcp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SERVER\SynologyDrive\HBV\Reports\rcp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5505F3E4-4EEE-4D42-BF85-DDB7C12BF6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7654102D-F3E0-449C-B993-ABC675820F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="946" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="946" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAX-INVOICE A5" sheetId="58" r:id="rId1"/>
@@ -671,9 +671,6 @@
     <t>General</t>
   </si>
   <si>
-    <t>Tel/Telegram: 012 278 096/ 096 5 306 143</t>
-  </si>
-  <si>
     <t xml:space="preserve">Customer Name and Signature </t>
   </si>
   <si>
@@ -704,6 +701,9 @@
   </si>
   <si>
     <t>EXCHANGE RATE:</t>
+  </si>
+  <si>
+    <t>Tel/Telegram: 012 278 794</t>
   </si>
 </sst>
 </file>
@@ -730,7 +730,7 @@
     <numFmt numFmtId="178" formatCode="dd\-mm\-yy"/>
     <numFmt numFmtId="179" formatCode="\៛#,##0;\-\៛#,##0"/>
   </numFmts>
-  <fonts count="76">
+  <fonts count="80">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1182,20 +1182,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="8"/>
-      <name val="Khmer OS Muol"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Khmer OS Battambang"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="8"/>
-      <name val="Khmer OS Muol Light"/>
     </font>
     <font>
       <b/>
@@ -1216,23 +1205,59 @@
     <font>
       <b/>
       <u val="double"/>
-      <sz val="6"/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Khmer OS Battambang"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Khmer OS Muol Light"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Khmer OS Muol"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Khmer OS Battambang"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <u val="double"/>
+      <sz val="8"/>
       <color indexed="8"/>
       <name val="Khmer OS Battambang"/>
     </font>
     <font>
       <b/>
-      <u val="double"/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+      <color indexed="8"/>
       <name val="Khmer OS Battambang"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <color indexed="8"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <scheme val="major"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <u val="double"/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Khmer OS Battambang"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1654,7 +1679,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="325">
+  <cellXfs count="328">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2417,123 +2442,81 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="67" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="9" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="9" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="67" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="67" fillId="0" borderId="20" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="9" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="20" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="68" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="9" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="9" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="68" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="68" fillId="0" borderId="20" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="75" fillId="11" borderId="17" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="9" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="20" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="7" fontId="70" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="70" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="70" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="70" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="74" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="74" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2629,6 +2612,57 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="11" borderId="17" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="77" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="77" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="77" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="77" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="79" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="79" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="30">
@@ -2694,71 +2728,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>255390</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="A close-up of a globe&#10;&#10;AI-generated content may be incorrect.">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D520BEC1-FBC0-4CC0-AC8F-3FA676A314ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="82550" y="82550"/>
-          <a:ext cx="679450" cy="687190"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1048562</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4095</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>77010</xdr:rowOff>
+      <xdr:rowOff>37597</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>428420</xdr:colOff>
+      <xdr:colOff>448126</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>161184</xdr:rowOff>
+      <xdr:rowOff>82356</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2774,7 +2753,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2788,8 +2767,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1210690" y="5277255"/>
-          <a:ext cx="980868" cy="927237"/>
+          <a:off x="1232492" y="5470131"/>
+          <a:ext cx="976117" cy="925001"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2883,6 +2862,61 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>6568</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>925990</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>71016</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BDCD65A-1F4A-481A-BD63-4506A2473ABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1" y="6568"/>
+          <a:ext cx="1090213" cy="1260000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3330,7 +3364,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" style="253" customWidth="1"/>
@@ -3344,53 +3378,53 @@
     <col min="9" max="16384" width="9.140625" style="253"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5">
-      <c r="A1" s="273" t="s">
+    <row r="1" spans="1:8" ht="21">
+      <c r="A1" s="311" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="273"/>
-      <c r="C1" s="273"/>
-      <c r="D1" s="273"/>
-      <c r="E1" s="273"/>
-      <c r="F1" s="273"/>
-      <c r="G1" s="273"/>
-      <c r="H1" s="273"/>
-    </row>
-    <row r="2" spans="1:8" ht="21">
-      <c r="A2" s="274" t="s">
+      <c r="B1" s="311"/>
+      <c r="C1" s="311"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+    </row>
+    <row r="2" spans="1:8" ht="21.75">
+      <c r="A2" s="312" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="274"/>
-      <c r="C2" s="274"/>
-      <c r="D2" s="274"/>
-      <c r="E2" s="274"/>
-      <c r="F2" s="274"/>
-      <c r="G2" s="274"/>
-      <c r="H2" s="274"/>
+      <c r="B2" s="312"/>
+      <c r="C2" s="312"/>
+      <c r="D2" s="312"/>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="312"/>
     </row>
     <row r="3" spans="1:8" ht="33" customHeight="1">
-      <c r="A3" s="275" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="276"/>
-      <c r="C3" s="276"/>
-      <c r="D3" s="276"/>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
-      <c r="G3" s="276"/>
-      <c r="H3" s="276"/>
+      <c r="A3" s="270" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="271"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="271"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
-      <c r="A4" s="277" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="277"/>
-      <c r="C4" s="277"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
-      <c r="F4" s="277"/>
-      <c r="G4" s="277"/>
-      <c r="H4" s="277"/>
+      <c r="A4" s="272" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="272"/>
+      <c r="C4" s="272"/>
+      <c r="D4" s="272"/>
+      <c r="E4" s="272"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="272"/>
+      <c r="H4" s="272"/>
     </row>
     <row r="5" spans="1:8" ht="26.25" customHeight="1">
       <c r="A5" s="256"/>
@@ -3403,300 +3437,304 @@
       <c r="H5" s="255"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="254" t="s">
+      <c r="A6" s="313" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="254"/>
-      <c r="C6" s="254"/>
-      <c r="D6" s="254"/>
-      <c r="E6" s="254"/>
-      <c r="F6" s="254"/>
-      <c r="G6" s="254"/>
-      <c r="H6" s="254"/>
+      <c r="B6" s="313"/>
+      <c r="C6" s="313"/>
+      <c r="D6" s="313"/>
+      <c r="E6" s="313"/>
+      <c r="F6" s="313"/>
+      <c r="G6" s="313"/>
+      <c r="H6" s="313"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="254"/>
-      <c r="B7" s="279" t="s">
+      <c r="A7" s="313"/>
+      <c r="B7" s="314" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="279"/>
-      <c r="D7" s="279"/>
-      <c r="E7" s="279"/>
-      <c r="F7" s="280" t="s">
+      <c r="C7" s="314"/>
+      <c r="D7" s="314"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="315" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="280"/>
-      <c r="H7" s="280"/>
+      <c r="G7" s="315"/>
+      <c r="H7" s="315"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="254" t="s">
+      <c r="A8" s="313" t="s">
         <v>158</v>
       </c>
-      <c r="B8" s="254"/>
-      <c r="C8" s="254"/>
-      <c r="D8" s="254"/>
-      <c r="E8" s="254"/>
-      <c r="F8" s="254"/>
-      <c r="G8" s="254"/>
-      <c r="H8" s="254"/>
+      <c r="B8" s="313"/>
+      <c r="C8" s="313"/>
+      <c r="D8" s="313"/>
+      <c r="E8" s="313"/>
+      <c r="F8" s="313"/>
+      <c r="G8" s="313"/>
+      <c r="H8" s="313"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="254"/>
-      <c r="B9" s="279" t="s">
+      <c r="A9" s="313"/>
+      <c r="B9" s="314" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="314"/>
+      <c r="D9" s="314"/>
+      <c r="E9" s="314"/>
+      <c r="F9" s="315" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="315"/>
+      <c r="H9" s="315"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="313" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="313"/>
+      <c r="C10" s="313"/>
+      <c r="D10" s="313"/>
+      <c r="E10" s="313"/>
+      <c r="F10" s="313"/>
+      <c r="G10" s="313"/>
+      <c r="H10" s="313"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="313"/>
+      <c r="B11" s="316" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="316"/>
+      <c r="D11" s="316"/>
+      <c r="E11" s="316"/>
+      <c r="F11" s="313"/>
+      <c r="G11" s="313"/>
+      <c r="H11" s="313"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A12" s="317" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="317" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="317" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="279"/>
-      <c r="D9" s="279"/>
-      <c r="E9" s="279"/>
-      <c r="F9" s="280" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="254" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="254"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="254"/>
-      <c r="G10" s="254"/>
-      <c r="H10" s="254"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="254"/>
-      <c r="B11" s="278" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="278"/>
-      <c r="D11" s="278"/>
-      <c r="E11" s="278"/>
-      <c r="F11" s="254"/>
-      <c r="G11" s="254"/>
-      <c r="H11" s="254"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A12" s="269" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="269" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="269" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="269" t="s">
+      <c r="D12" s="317" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="269" t="s">
+      <c r="E12" s="317" t="s">
         <v>163</v>
       </c>
-      <c r="F12" s="270" t="s">
+      <c r="F12" s="318" t="s">
         <v>164</v>
       </c>
-      <c r="G12" s="270" t="s">
+      <c r="G12" s="318" t="s">
         <v>165</v>
       </c>
-      <c r="H12" s="270" t="s">
+      <c r="H12" s="318" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5">
-      <c r="A13" s="259"/>
-      <c r="B13" s="260"/>
-      <c r="C13" s="261"/>
-      <c r="D13" s="262"/>
-      <c r="E13" s="262"/>
-      <c r="F13" s="263"/>
-      <c r="G13" s="271"/>
-      <c r="H13" s="264"/>
+      <c r="A13" s="258"/>
+      <c r="B13" s="259"/>
+      <c r="C13" s="260"/>
+      <c r="D13" s="261"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="268"/>
+      <c r="H13" s="263"/>
     </row>
     <row r="14" spans="1:8" ht="16.5">
-      <c r="A14" s="262"/>
-      <c r="B14" s="260"/>
-      <c r="C14" s="261"/>
-      <c r="D14" s="262"/>
-      <c r="E14" s="262"/>
-      <c r="F14" s="263"/>
-      <c r="G14" s="271"/>
-      <c r="H14" s="264"/>
+      <c r="A14" s="261"/>
+      <c r="B14" s="259"/>
+      <c r="C14" s="260"/>
+      <c r="D14" s="261"/>
+      <c r="E14" s="261"/>
+      <c r="F14" s="262"/>
+      <c r="G14" s="268"/>
+      <c r="H14" s="263"/>
     </row>
     <row r="15" spans="1:8" ht="16.5">
-      <c r="A15" s="262"/>
-      <c r="B15" s="260"/>
-      <c r="C15" s="261"/>
-      <c r="D15" s="262"/>
-      <c r="E15" s="262"/>
-      <c r="F15" s="263"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="264"/>
+      <c r="A15" s="261"/>
+      <c r="B15" s="259"/>
+      <c r="C15" s="260"/>
+      <c r="D15" s="261"/>
+      <c r="E15" s="261"/>
+      <c r="F15" s="262"/>
+      <c r="G15" s="268"/>
+      <c r="H15" s="263"/>
     </row>
     <row r="16" spans="1:8" ht="16.5">
-      <c r="A16" s="262"/>
-      <c r="B16" s="260"/>
-      <c r="C16" s="261"/>
-      <c r="D16" s="262"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="263"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="264"/>
-    </row>
-    <row r="17" spans="1:8" ht="16.5">
-      <c r="A17" s="262"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="261"/>
-      <c r="D17" s="262"/>
-      <c r="E17" s="262"/>
-      <c r="F17" s="263"/>
-      <c r="G17" s="271"/>
-      <c r="H17" s="264"/>
-    </row>
-    <row r="18" spans="1:8" ht="16.5">
-      <c r="A18" s="262"/>
-      <c r="B18" s="260"/>
-      <c r="C18" s="261"/>
-      <c r="D18" s="262"/>
-      <c r="E18" s="262"/>
-      <c r="F18" s="263"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="264"/>
-    </row>
-    <row r="19" spans="1:8" ht="16.5">
-      <c r="A19" s="262"/>
-      <c r="B19" s="260"/>
-      <c r="C19" s="261"/>
-      <c r="D19" s="262"/>
-      <c r="E19" s="262"/>
-      <c r="F19" s="263"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="264"/>
-    </row>
-    <row r="20" spans="1:8" ht="16.5">
-      <c r="A20" s="262"/>
-      <c r="B20" s="260"/>
-      <c r="C20" s="261"/>
-      <c r="D20" s="262"/>
-      <c r="E20" s="262"/>
-      <c r="F20" s="263"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="264"/>
-    </row>
-    <row r="21" spans="1:8" ht="16.5">
-      <c r="A21" s="262"/>
-      <c r="B21" s="260"/>
-      <c r="C21" s="261"/>
-      <c r="D21" s="262"/>
-      <c r="E21" s="262"/>
-      <c r="F21" s="263"/>
-      <c r="G21" s="271"/>
-      <c r="H21" s="264"/>
-    </row>
-    <row r="22" spans="1:8" ht="16.5">
-      <c r="A22" s="262"/>
-      <c r="B22" s="260"/>
-      <c r="C22" s="261"/>
-      <c r="D22" s="262"/>
-      <c r="E22" s="262"/>
-      <c r="F22" s="263"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="264"/>
-    </row>
-    <row r="23" spans="1:8" ht="16.5">
-      <c r="A23" s="262"/>
-      <c r="B23" s="260"/>
-      <c r="C23" s="261"/>
-      <c r="D23" s="262"/>
-      <c r="E23" s="262"/>
-      <c r="F23" s="263"/>
-      <c r="G23" s="271"/>
-      <c r="H23" s="264"/>
-    </row>
-    <row r="24" spans="1:8" ht="16.5">
-      <c r="A24" s="265"/>
-      <c r="B24" s="266"/>
-      <c r="C24" s="267"/>
-      <c r="D24" s="265"/>
-      <c r="E24" s="265"/>
-      <c r="F24" s="268"/>
-      <c r="G24" s="272"/>
-      <c r="H24" s="264"/>
-    </row>
-    <row r="25" spans="1:8" ht="16.5">
+      <c r="A16" s="261"/>
+      <c r="B16" s="259"/>
+      <c r="C16" s="260"/>
+      <c r="D16" s="261"/>
+      <c r="E16" s="261"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="268"/>
+      <c r="H16" s="263"/>
+    </row>
+    <row r="17" spans="1:9" ht="16.5">
+      <c r="A17" s="261"/>
+      <c r="B17" s="259"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="261"/>
+      <c r="E17" s="261"/>
+      <c r="F17" s="262"/>
+      <c r="G17" s="268"/>
+      <c r="H17" s="263"/>
+    </row>
+    <row r="18" spans="1:9" ht="16.5">
+      <c r="A18" s="261"/>
+      <c r="B18" s="259"/>
+      <c r="C18" s="260"/>
+      <c r="D18" s="261"/>
+      <c r="E18" s="261"/>
+      <c r="F18" s="262"/>
+      <c r="G18" s="268"/>
+      <c r="H18" s="263"/>
+    </row>
+    <row r="19" spans="1:9" ht="16.5">
+      <c r="A19" s="261"/>
+      <c r="B19" s="259"/>
+      <c r="C19" s="260"/>
+      <c r="D19" s="261"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="262"/>
+      <c r="G19" s="268"/>
+      <c r="H19" s="263"/>
+    </row>
+    <row r="20" spans="1:9" ht="16.5">
+      <c r="A20" s="261"/>
+      <c r="B20" s="259"/>
+      <c r="C20" s="260"/>
+      <c r="D20" s="261"/>
+      <c r="E20" s="261"/>
+      <c r="F20" s="262"/>
+      <c r="G20" s="268"/>
+      <c r="H20" s="263"/>
+    </row>
+    <row r="21" spans="1:9" ht="16.5">
+      <c r="A21" s="261"/>
+      <c r="B21" s="259"/>
+      <c r="C21" s="260"/>
+      <c r="D21" s="261"/>
+      <c r="E21" s="261"/>
+      <c r="F21" s="262"/>
+      <c r="G21" s="268"/>
+      <c r="H21" s="263"/>
+    </row>
+    <row r="22" spans="1:9" ht="16.5">
+      <c r="A22" s="261"/>
+      <c r="B22" s="259"/>
+      <c r="C22" s="260"/>
+      <c r="D22" s="261"/>
+      <c r="E22" s="261"/>
+      <c r="F22" s="262"/>
+      <c r="G22" s="268"/>
+      <c r="H22" s="263"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5">
+      <c r="A23" s="261"/>
+      <c r="B23" s="259"/>
+      <c r="C23" s="260"/>
+      <c r="D23" s="261"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="268"/>
+      <c r="H23" s="263"/>
+    </row>
+    <row r="24" spans="1:9" ht="16.5">
+      <c r="A24" s="264"/>
+      <c r="B24" s="265"/>
+      <c r="C24" s="266"/>
+      <c r="D24" s="264"/>
+      <c r="E24" s="264"/>
+      <c r="F24" s="267"/>
+      <c r="G24" s="269"/>
+      <c r="H24" s="263"/>
+    </row>
+    <row r="25" spans="1:9" ht="19.5">
       <c r="A25" s="254"/>
-      <c r="B25" s="258" t="s">
+      <c r="B25" s="319" t="s">
         <v>167</v>
       </c>
       <c r="C25" s="254"/>
       <c r="D25" s="254"/>
-      <c r="E25" s="289" t="s">
-        <v>178</v>
-      </c>
-      <c r="F25" s="289"/>
-      <c r="G25" s="283">
+      <c r="E25" s="273" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="273"/>
+      <c r="G25" s="320">
         <f>SUM(H13:H24)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="284"/>
-    </row>
-    <row r="26" spans="1:8" ht="16.5" customHeight="1">
+      <c r="H25" s="321"/>
+      <c r="I25" s="322"/>
+    </row>
+    <row r="26" spans="1:9" ht="16.5" customHeight="1">
       <c r="A26" s="254"/>
-      <c r="B26" s="257" t="s">
+      <c r="B26" s="254" t="s">
         <v>168</v>
       </c>
       <c r="C26" s="254"/>
-      <c r="D26" s="289" t="s">
-        <v>181</v>
-      </c>
-      <c r="E26" s="289"/>
-      <c r="F26" s="289"/>
-      <c r="G26" s="285">
+      <c r="D26" s="273" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="273"/>
+      <c r="F26" s="273"/>
+      <c r="G26" s="323">
         <v>0</v>
       </c>
-      <c r="H26" s="286"/>
-    </row>
-    <row r="27" spans="1:8" ht="16.5" customHeight="1">
+      <c r="H26" s="324"/>
+      <c r="I26" s="322"/>
+    </row>
+    <row r="27" spans="1:9" ht="16.5" customHeight="1">
       <c r="A27" s="254"/>
-      <c r="B27" s="282" t="s">
-        <v>177</v>
+      <c r="B27" s="275" t="s">
+        <v>176</v>
       </c>
       <c r="C27" s="254"/>
-      <c r="D27" s="289" t="s">
-        <v>179</v>
-      </c>
-      <c r="E27" s="289"/>
-      <c r="F27" s="289"/>
-      <c r="G27" s="291">
+      <c r="D27" s="273" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="273"/>
+      <c r="F27" s="273"/>
+      <c r="G27" s="325">
         <f>G25*G26</f>
         <v>0</v>
       </c>
-      <c r="H27" s="292"/>
-    </row>
-    <row r="28" spans="1:8" ht="16.5" customHeight="1">
+      <c r="H27" s="326"/>
+      <c r="I27" s="322"/>
+    </row>
+    <row r="28" spans="1:9" ht="16.5" customHeight="1">
       <c r="A28" s="254"/>
-      <c r="B28" s="282"/>
+      <c r="B28" s="275"/>
       <c r="C28" s="254"/>
-      <c r="D28" s="289"/>
-      <c r="E28" s="289"/>
-      <c r="F28" s="289"/>
-      <c r="G28" s="290"/>
-      <c r="H28" s="290"/>
-    </row>
-    <row r="29" spans="1:8" ht="16.5" customHeight="1">
+      <c r="D28" s="315"/>
+      <c r="E28" s="315"/>
+      <c r="F28" s="315"/>
+      <c r="G28" s="327"/>
+      <c r="H28" s="327"/>
+      <c r="I28" s="322"/>
+    </row>
+    <row r="29" spans="1:9" ht="16.5" customHeight="1">
       <c r="A29" s="254"/>
       <c r="B29" s="257" t="s">
         <v>169</v>
       </c>
       <c r="C29" s="254"/>
-      <c r="D29" s="289"/>
-      <c r="E29" s="289"/>
-      <c r="F29" s="289"/>
-      <c r="G29" s="288"/>
-      <c r="H29" s="288"/>
-    </row>
-    <row r="30" spans="1:8" ht="16.5">
+      <c r="D29" s="278"/>
+      <c r="E29" s="278"/>
+      <c r="F29" s="278"/>
+      <c r="G29" s="277"/>
+      <c r="H29" s="277"/>
+    </row>
+    <row r="30" spans="1:9" ht="16.5">
       <c r="A30" s="254"/>
       <c r="B30" s="254"/>
       <c r="C30" s="254"/>
@@ -3706,7 +3744,7 @@
       <c r="G30" s="254"/>
       <c r="H30" s="254"/>
     </row>
-    <row r="31" spans="1:8" ht="16.5">
+    <row r="31" spans="1:9" ht="16.5">
       <c r="A31" s="254"/>
       <c r="B31" s="254"/>
       <c r="C31" s="254"/>
@@ -3716,33 +3754,33 @@
       <c r="G31" s="254"/>
       <c r="H31" s="254"/>
     </row>
-    <row r="32" spans="1:8" ht="16.5">
+    <row r="32" spans="1:9" ht="16.5">
       <c r="A32" s="254"/>
-      <c r="B32" s="287" t="s">
-        <v>172</v>
-      </c>
-      <c r="C32" s="287"/>
+      <c r="B32" s="276" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="276"/>
       <c r="D32" s="254"/>
       <c r="E32" s="254"/>
-      <c r="F32" s="287" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="287"/>
-      <c r="H32" s="287"/>
+      <c r="F32" s="276" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" s="276"/>
+      <c r="H32" s="276"/>
     </row>
     <row r="33" spans="1:8" ht="16.5">
       <c r="A33" s="254"/>
-      <c r="B33" s="281" t="s">
+      <c r="B33" s="274" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="281"/>
+      <c r="C33" s="274"/>
       <c r="D33" s="254"/>
       <c r="E33" s="254"/>
-      <c r="F33" s="281" t="s">
+      <c r="F33" s="274" t="s">
         <v>4</v>
       </c>
-      <c r="G33" s="281"/>
-      <c r="H33" s="281"/>
+      <c r="G33" s="274"/>
+      <c r="H33" s="274"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3781,7 +3819,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="11" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -3820,52 +3858,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="279" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
+      <c r="H1" s="279"/>
+      <c r="I1" s="279"/>
+      <c r="J1" s="279"/>
+      <c r="K1" s="279"/>
       <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="294" t="s">
+      <c r="A2" s="280" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="294"/>
-      <c r="C2" s="294"/>
-      <c r="D2" s="294"/>
-      <c r="E2" s="294"/>
-      <c r="F2" s="294"/>
-      <c r="G2" s="294"/>
-      <c r="H2" s="294"/>
-      <c r="I2" s="294"/>
-      <c r="J2" s="294"/>
-      <c r="K2" s="294"/>
+      <c r="B2" s="280"/>
+      <c r="C2" s="280"/>
+      <c r="D2" s="280"/>
+      <c r="E2" s="280"/>
+      <c r="F2" s="280"/>
+      <c r="G2" s="280"/>
+      <c r="H2" s="280"/>
+      <c r="I2" s="280"/>
+      <c r="J2" s="280"/>
+      <c r="K2" s="280"/>
       <c r="L2" s="29"/>
     </row>
     <row r="3" spans="1:26" ht="45" customHeight="1">
-      <c r="A3" s="295" t="s">
+      <c r="A3" s="281" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="295"/>
-      <c r="C3" s="295"/>
-      <c r="D3" s="295"/>
-      <c r="E3" s="295"/>
-      <c r="F3" s="295"/>
-      <c r="G3" s="295"/>
-      <c r="H3" s="295"/>
-      <c r="I3" s="295"/>
-      <c r="J3" s="295"/>
-      <c r="K3" s="295"/>
-      <c r="L3" s="295"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="281"/>
+      <c r="D3" s="281"/>
+      <c r="E3" s="281"/>
+      <c r="F3" s="281"/>
+      <c r="G3" s="281"/>
+      <c r="H3" s="281"/>
+      <c r="I3" s="281"/>
+      <c r="J3" s="281"/>
+      <c r="K3" s="281"/>
+      <c r="L3" s="281"/>
     </row>
     <row r="4" spans="1:26" s="10" customFormat="1" ht="34.9" customHeight="1">
       <c r="A4" s="24" t="s">
@@ -3952,15 +3990,15 @@
       <c r="V5" s="106"/>
     </row>
     <row r="6" spans="1:26" ht="50.25" customHeight="1">
-      <c r="A6" s="311">
+      <c r="A6" s="297">
         <v>45898</v>
       </c>
-      <c r="B6" s="309" t="s">
+      <c r="B6" s="295" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="307"/>
-      <c r="D6" s="305"/>
-      <c r="E6" s="303" t="s">
+      <c r="C6" s="293"/>
+      <c r="D6" s="291"/>
+      <c r="E6" s="289" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="119" t="s">
@@ -3988,11 +4026,11 @@
       <c r="U6" s="120"/>
     </row>
     <row r="7" spans="1:26" ht="54.75" customHeight="1">
-      <c r="A7" s="312"/>
-      <c r="B7" s="310"/>
-      <c r="C7" s="308"/>
-      <c r="D7" s="306"/>
-      <c r="E7" s="304"/>
+      <c r="A7" s="298"/>
+      <c r="B7" s="296"/>
+      <c r="C7" s="294"/>
+      <c r="D7" s="292"/>
+      <c r="E7" s="290"/>
       <c r="F7" s="119" t="s">
         <v>137</v>
       </c>
@@ -4372,15 +4410,15 @@
       <c r="U19" s="121"/>
     </row>
     <row r="20" spans="1:26" ht="34.9" customHeight="1">
-      <c r="A20" s="298" t="s">
+      <c r="A20" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="298"/>
-      <c r="C20" s="298"/>
-      <c r="D20" s="298"/>
-      <c r="E20" s="298"/>
-      <c r="F20" s="298"/>
-      <c r="G20" s="298"/>
+      <c r="B20" s="284"/>
+      <c r="C20" s="284"/>
+      <c r="D20" s="284"/>
+      <c r="E20" s="284"/>
+      <c r="F20" s="284"/>
+      <c r="G20" s="284"/>
       <c r="H20" s="6">
         <f>SUM(H6:H19)</f>
         <v>0</v>
@@ -4442,11 +4480,11 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" spans="1:26" s="17" customFormat="1" ht="25.15" customHeight="1">
-      <c r="A22" s="299" t="s">
+      <c r="A22" s="285" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="299"/>
-      <c r="C22" s="299"/>
+      <c r="B22" s="285"/>
+      <c r="C22" s="285"/>
       <c r="D22" s="153"/>
       <c r="E22" s="154" t="s">
         <v>39</v>
@@ -4455,10 +4493,10 @@
       <c r="G22" s="30"/>
       <c r="H22" s="37"/>
       <c r="I22" s="116"/>
-      <c r="J22" s="302" t="s">
+      <c r="J22" s="288" t="s">
         <v>43</v>
       </c>
-      <c r="K22" s="302"/>
+      <c r="K22" s="288"/>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
     </row>
@@ -4557,10 +4595,10 @@
       <c r="A28" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="301">
+      <c r="B28" s="287">
         <v>45916</v>
       </c>
-      <c r="C28" s="301"/>
+      <c r="C28" s="287"/>
       <c r="D28" s="36"/>
       <c r="E28" s="71" t="s">
         <v>4</v>
@@ -4631,12 +4669,12 @@
       <c r="D32" s="36"/>
       <c r="E32" s="38"/>
       <c r="F32" s="38"/>
-      <c r="G32" s="300" t="str">
+      <c r="G32" s="286" t="str">
         <f>A3</f>
         <v>ACCOUNT LEDGER FOR AUGUST 2019</v>
       </c>
-      <c r="H32" s="300"/>
-      <c r="I32" s="300"/>
+      <c r="H32" s="286"/>
+      <c r="I32" s="286"/>
       <c r="J32" s="44"/>
       <c r="K32" s="43"/>
     </row>
@@ -5366,8 +5404,8 @@
       <c r="B73" s="66"/>
       <c r="C73" s="39"/>
       <c r="D73" s="36"/>
-      <c r="E73" s="296"/>
-      <c r="F73" s="297"/>
+      <c r="E73" s="282"/>
+      <c r="F73" s="283"/>
       <c r="G73" s="62" t="s">
         <v>152</v>
       </c>
@@ -5714,36 +5752,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="34.5" customHeight="1">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="302" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
+      <c r="B1" s="302"/>
+      <c r="C1" s="302"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="302"/>
+      <c r="H1" s="302"/>
+      <c r="I1" s="302"/>
+      <c r="J1" s="302"/>
+      <c r="K1" s="302"/>
+      <c r="L1" s="302"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1">
-      <c r="A2" s="317" t="s">
+      <c r="A2" s="303" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="317"/>
-      <c r="C2" s="317"/>
-      <c r="D2" s="317"/>
-      <c r="E2" s="317"/>
-      <c r="F2" s="317"/>
-      <c r="G2" s="317"/>
-      <c r="H2" s="317"/>
-      <c r="I2" s="317"/>
-      <c r="J2" s="317"/>
-      <c r="K2" s="317"/>
-      <c r="L2" s="317"/>
+      <c r="B2" s="303"/>
+      <c r="C2" s="303"/>
+      <c r="D2" s="303"/>
+      <c r="E2" s="303"/>
+      <c r="F2" s="303"/>
+      <c r="G2" s="303"/>
+      <c r="H2" s="303"/>
+      <c r="I2" s="303"/>
+      <c r="J2" s="303"/>
+      <c r="K2" s="303"/>
+      <c r="L2" s="303"/>
     </row>
     <row r="3" spans="1:16" s="159" customFormat="1" ht="32.65" customHeight="1">
       <c r="A3" s="156" t="s">
@@ -5980,15 +6018,15 @@
       <c r="L9" s="241"/>
     </row>
     <row r="10" spans="1:16" s="192" customFormat="1" ht="31.9" customHeight="1">
-      <c r="A10" s="318" t="s">
+      <c r="A10" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="318"/>
-      <c r="C10" s="318"/>
-      <c r="D10" s="318"/>
-      <c r="E10" s="318"/>
-      <c r="F10" s="318"/>
-      <c r="G10" s="318"/>
+      <c r="B10" s="304"/>
+      <c r="C10" s="304"/>
+      <c r="D10" s="304"/>
+      <c r="E10" s="304"/>
+      <c r="F10" s="304"/>
+      <c r="G10" s="304"/>
       <c r="H10" s="188">
         <f>SUM(H5:H9)</f>
         <v>1280</v>
@@ -6039,10 +6077,10 @@
       <c r="J12" s="194"/>
       <c r="K12" s="194"/>
       <c r="L12" s="194"/>
-      <c r="M12" s="319" t="s">
+      <c r="M12" s="305" t="s">
         <v>101</v>
       </c>
-      <c r="N12" s="319"/>
+      <c r="N12" s="305"/>
     </row>
     <row r="13" spans="1:16" s="197" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A13" s="200"/>
@@ -6122,10 +6160,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="204"/>
-      <c r="C17" s="320">
+      <c r="C17" s="306">
         <v>45076</v>
       </c>
-      <c r="D17" s="320"/>
+      <c r="D17" s="306"/>
       <c r="E17" s="194"/>
       <c r="F17" s="204" t="s">
         <v>127</v>
@@ -6160,13 +6198,13 @@
       <c r="D19" s="209"/>
       <c r="E19" s="194"/>
       <c r="F19" s="194"/>
-      <c r="G19" s="313" t="str">
+      <c r="G19" s="299" t="str">
         <f>A2</f>
         <v>PETTY CASH OF URATA-MANAGEMENT FOR MAY 2023 (UM)</v>
       </c>
-      <c r="H19" s="314"/>
-      <c r="I19" s="314"/>
-      <c r="J19" s="315"/>
+      <c r="H19" s="300"/>
+      <c r="I19" s="300"/>
+      <c r="J19" s="301"/>
       <c r="K19" s="194"/>
       <c r="L19" s="194"/>
     </row>
@@ -7840,26 +7878,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="293" t="s">
+      <c r="A1" s="279" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
+      <c r="B1" s="279"/>
+      <c r="C1" s="279"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
+      <c r="F1" s="279"/>
+      <c r="G1" s="279"/>
     </row>
     <row r="2" spans="1:13" ht="49.9" customHeight="1">
-      <c r="A2" s="295" t="s">
+      <c r="A2" s="281" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="295"/>
-      <c r="C2" s="295"/>
-      <c r="D2" s="295"/>
-      <c r="E2" s="295"/>
-      <c r="F2" s="295"/>
-      <c r="G2" s="295"/>
+      <c r="B2" s="281"/>
+      <c r="C2" s="281"/>
+      <c r="D2" s="281"/>
+      <c r="E2" s="281"/>
+      <c r="F2" s="281"/>
+      <c r="G2" s="281"/>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="34.9" customHeight="1">
       <c r="A3" s="95" t="s">
@@ -8276,14 +8314,14 @@
       <c r="M28" s="75"/>
     </row>
     <row r="29" spans="1:13" ht="34.9" customHeight="1">
-      <c r="A29" s="323" t="s">
+      <c r="A29" s="309" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="323"/>
-      <c r="C29" s="323"/>
-      <c r="D29" s="323"/>
-      <c r="E29" s="323"/>
-      <c r="F29" s="323"/>
+      <c r="B29" s="309"/>
+      <c r="C29" s="309"/>
+      <c r="D29" s="309"/>
+      <c r="E29" s="309"/>
+      <c r="F29" s="309"/>
       <c r="G29" s="74">
         <f>SUM(G4:G28)</f>
         <v>0</v>
@@ -8311,11 +8349,11 @@
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13" s="17" customFormat="1" ht="25.15" customHeight="1">
-      <c r="A31" s="324" t="s">
+      <c r="A31" s="310" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="324"/>
-      <c r="C31" s="324"/>
+      <c r="B31" s="310"/>
+      <c r="C31" s="310"/>
       <c r="D31" s="36"/>
       <c r="F31" s="37" t="s">
         <v>39</v>
@@ -8365,8 +8403,8 @@
       <c r="A36" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="301"/>
-      <c r="C36" s="301"/>
+      <c r="B36" s="287"/>
+      <c r="C36" s="287"/>
       <c r="D36" s="36"/>
       <c r="F36" s="71" t="s">
         <v>4</v>
@@ -8386,11 +8424,11 @@
       <c r="A38" s="39"/>
       <c r="B38" s="39"/>
       <c r="C38" s="39"/>
-      <c r="D38" s="321" t="str">
+      <c r="D38" s="307" t="str">
         <f>A2</f>
         <v>EXPENSES REIMBURSEMENT FOR JANUARY 2022</v>
       </c>
-      <c r="E38" s="322"/>
+      <c r="E38" s="308"/>
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
     </row>
